--- a/data/trans_orig/P36BPD04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023</t>
+          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37542</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>43979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72484</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89638</t>
+          <t>88663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132378</t>
+          <t>130368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75133</t>
+          <t>76483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104631</t>
+          <t>105110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175249</t>
+          <t>172725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226633</t>
+          <t>227547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>315934</t>
+          <t>316824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>372816</t>
+          <t>373223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>376095</t>
+          <t>374818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>416481</t>
+          <t>417196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>707229</t>
+          <t>706079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>775812</t>
+          <t>772621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137189</t>
+          <t>135037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189232</t>
+          <t>187901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141056</t>
+          <t>140591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175260</t>
+          <t>176118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285362</t>
+          <t>286053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348582</t>
+          <t>351076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57522</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>115056</t>
+          <t>115285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84302</t>
+          <t>78156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206344</t>
+          <t>205363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107663</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>146466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183696</t>
+          <t>192788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329279</t>
+          <t>332061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>702174</t>
+          <t>699095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>988167</t>
+          <t>1003518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588128</t>
+          <t>586255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641574</t>
+          <t>638967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1322757</t>
+          <t>1317913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1683614</t>
+          <t>1656079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94649</t>
+          <t>87547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227899</t>
+          <t>229173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>165583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>207066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>219898</t>
+          <t>235704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>417169</t>
+          <t>416158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>77895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62594</t>
+          <t>64344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>555569</t>
+          <t>586818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122212</t>
+          <t>118789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747813</t>
+          <t>736527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119912</t>
+          <t>119837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170974</t>
+          <t>169923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68379</t>
+          <t>65057</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>176514</t>
+          <t>176435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185896</t>
+          <t>184473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>325525</t>
+          <t>328014</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>336704</t>
+          <t>334112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>397184</t>
+          <t>396254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>205354</t>
+          <t>188898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>512032</t>
+          <t>509690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>520369</t>
+          <t>502546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>879042</t>
+          <t>876319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>115892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162189</t>
+          <t>163557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79604</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232877</t>
+          <t>243177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201798</t>
+          <t>194571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378360</t>
+          <t>378459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54598</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92650</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46449</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78766</t>
+          <t>80988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111483</t>
+          <t>111315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163641</t>
+          <t>164027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175305</t>
+          <t>174999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233024</t>
+          <t>233181</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>146843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213354</t>
+          <t>212975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335175</t>
+          <t>336820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430539</t>
+          <t>429409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>465788</t>
+          <t>462333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>535592</t>
+          <t>525173</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>583582</t>
+          <t>580515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>730369</t>
+          <t>721467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1069245</t>
+          <t>1070623</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1234273</t>
+          <t>1227156</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133719</t>
+          <t>134260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178708</t>
+          <t>179070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175136</t>
+          <t>176456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246042</t>
+          <t>249206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332503</t>
+          <t>331458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413728</t>
+          <t>412975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>254177</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180996</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>993277</t>
+          <t>1118414</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>383053</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1295234</t>
+          <t>1380234</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>467138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>674007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>431420</t>
+          <t>435251</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>581725</t>
+          <t>583919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>975893</t>
+          <t>974631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1230057</t>
+          <t>1244859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1877395</t>
+          <t>1894690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2302735</t>
+          <t>2369611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1653151</t>
+          <t>1615310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2176957</t>
+          <t>2174129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3720029</t>
+          <t>3688216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4317148</t>
+          <t>4347843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>484201</t>
+          <t>489481</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>696220</t>
+          <t>694271</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>594530</t>
+          <t>607721</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>812627</t>
+          <t>812179</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1177004</t>
+          <t>1157964</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1466550</t>
+          <t>1480467</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>44791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53735</t>
+          <t>57417</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40252</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>75648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>112963</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88663</t>
+          <t>95134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130368</t>
+          <t>137340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>89590</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>79771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105110</t>
+          <t>110710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>197461</t>
+          <t>207441</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172725</t>
+          <t>184706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227547</t>
+          <t>237151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>345235</t>
+          <t>376526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>316824</t>
+          <t>347643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>373223</t>
+          <t>406826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>396402</t>
+          <t>428830</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374818</t>
+          <t>405787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>417196</t>
+          <t>451511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>741636</t>
+          <t>805355</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>706079</t>
+          <t>768094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>772621</t>
+          <t>840418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>158796</t>
+          <t>176548</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135037</t>
+          <t>150500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187901</t>
+          <t>203486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156713</t>
+          <t>174090</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140591</t>
+          <t>157011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176118</t>
+          <t>194836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>315508</t>
+          <t>350638</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286053</t>
+          <t>321646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>351076</t>
+          <t>385668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>673928</t>
+          <t>731224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673928</t>
+          <t>731224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>673928</t>
+          <t>731224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1308340</t>
+          <t>1420851</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1308340</t>
+          <t>1420851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1308340</t>
+          <t>1420851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52771</t>
+          <t>46653</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>32822</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>63863</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>83853</t>
+          <t>80721</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>102455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154953</t>
+          <t>161331</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78156</t>
+          <t>137400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205363</t>
+          <t>187839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>125166</t>
+          <t>137806</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>118565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146466</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>280119</t>
+          <t>299137</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192788</t>
+          <t>267657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332061</t>
+          <t>332586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>812307</t>
+          <t>627003</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>589884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1003518</t>
+          <t>662681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>615399</t>
+          <t>687962</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>586255</t>
+          <t>658762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>638967</t>
+          <t>715097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1427706</t>
+          <t>1314965</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1317913</t>
+          <t>1266374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1656079</t>
+          <t>1359723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172834</t>
+          <t>213930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87547</t>
+          <t>184563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>229173</t>
+          <t>248150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185928</t>
+          <t>210457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165583</t>
+          <t>189278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207066</t>
+          <t>234777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>358762</t>
+          <t>424387</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>235704</t>
+          <t>387907</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>416158</t>
+          <t>464151</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957576</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957576</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957576</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150441</t>
+          <t>2119211</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150441</t>
+          <t>2119211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150441</t>
+          <t>2119211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>62825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41313</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77895</t>
+          <t>82228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>260851</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64344</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586818</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>317648</t>
+          <t>126474</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118789</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736527</t>
+          <t>151046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143122</t>
+          <t>159543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119837</t>
+          <t>133348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>187221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129666</t>
+          <t>144837</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65057</t>
+          <t>126034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>176435</t>
+          <t>165321</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>272788</t>
+          <t>304379</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>184473</t>
+          <t>272214</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>328014</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>367674</t>
+          <t>415943</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>334112</t>
+          <t>381972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>396254</t>
+          <t>453045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>383968</t>
+          <t>448548</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188898</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>509690</t>
+          <t>473421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>751642</t>
+          <t>864490</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502546</t>
+          <t>820789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>876319</t>
+          <t>904726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137086</t>
+          <t>164763</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115892</t>
+          <t>140446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163557</t>
+          <t>192819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>158881</t>
+          <t>155225</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83151</t>
+          <t>136244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243177</t>
+          <t>176065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>295967</t>
+          <t>319988</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194571</t>
+          <t>287946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378459</t>
+          <t>359044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>77172</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95900</t>
+          <t>99508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62851</t>
+          <t>69496</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80988</t>
+          <t>88812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>135143</t>
+          <t>146668</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111315</t>
+          <t>124262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164027</t>
+          <t>173716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202624</t>
+          <t>203810</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174999</t>
+          <t>176170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233181</t>
+          <t>233096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>186143</t>
+          <t>196723</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146843</t>
+          <t>175237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212975</t>
+          <t>219735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>388767</t>
+          <t>400532</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>336820</t>
+          <t>364569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429409</t>
+          <t>439494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>496628</t>
+          <t>535481</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>462333</t>
+          <t>501433</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>525173</t>
+          <t>569819</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>625194</t>
+          <t>619179</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>580515</t>
+          <t>586922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>721467</t>
+          <t>646366</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1121822</t>
+          <t>1154660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1070623</t>
+          <t>1111020</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1227156</t>
+          <t>1206275</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>155123</t>
+          <t>172482</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134260</t>
+          <t>148447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179070</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>219614</t>
+          <t>232503</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176456</t>
+          <t>208098</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249206</t>
+          <t>258244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>374737</t>
+          <t>404986</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331458</t>
+          <t>370338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>412975</t>
+          <t>439479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1093802</t>
+          <t>1117901</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1093802</t>
+          <t>1117901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1093802</t>
+          <t>1117901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2020469</t>
+          <t>2106846</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2020469</t>
+          <t>2106846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2020469</t>
+          <t>2106846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204371</t>
+          <t>210241</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>179966</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>247224</t>
+          <t>245850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>386008</t>
+          <t>201038</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181595</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1118414</t>
+          <t>230049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>590379</t>
+          <t>411279</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>379476</t>
+          <t>370773</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1380234</t>
+          <t>459581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>608570</t>
+          <t>637646</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>467138</t>
+          <t>587398</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>674007</t>
+          <t>691396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>530565</t>
+          <t>573844</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>435251</t>
+          <t>536409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>583919</t>
+          <t>621771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1139135</t>
+          <t>1211491</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>1150027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1244859</t>
+          <t>1281819</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2021844</t>
+          <t>1954952</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1894690</t>
+          <t>1895314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2369611</t>
+          <t>2032830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2020963</t>
+          <t>2184519</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1615310</t>
+          <t>2127672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2174129</t>
+          <t>2236697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4042807</t>
+          <t>4139471</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3688216</t>
+          <t>4048611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4347843</t>
+          <t>4219216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>623839</t>
+          <t>727723</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>489481</t>
+          <t>675106</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>694271</t>
+          <t>781812</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>721136</t>
+          <t>772276</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607721</t>
+          <t>730472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>812179</t>
+          <t>815131</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1344975</t>
+          <t>1499999</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1157964</t>
+          <t>1434999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1480467</t>
+          <t>1574613</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
